--- a/cuotas.xlsx
+++ b/cuotas.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="559" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="655" uniqueCount="159">
   <si>
     <t>Nombre</t>
   </si>
@@ -39,6 +39,9 @@
     <t>Mayo</t>
   </si>
   <si>
+    <t>Junio</t>
+  </si>
+  <si>
     <t>Alberty Quintana</t>
   </si>
   <si>
@@ -402,33 +405,54 @@
     <t>Trinidad Castillo</t>
   </si>
   <si>
+    <t>inostroza.se@gmail.com</t>
+  </si>
+  <si>
     <t>Martina Beltran</t>
   </si>
   <si>
     <t>Josefina Hernandez</t>
   </si>
   <si>
+    <t>eduardo.hernandez2988@gmail.com</t>
+  </si>
+  <si>
     <t>Benjamin Monsalve</t>
   </si>
   <si>
+    <t>rosamonsalve.b75@gmail.com</t>
+  </si>
+  <si>
     <t>Esteban Huentemil</t>
   </si>
   <si>
     <t>Matias Jara</t>
   </si>
   <si>
+    <t>rasalba1976@gmail.com</t>
+  </si>
+  <si>
     <t>Facundo Molina</t>
   </si>
   <si>
     <t>Maximo Perez</t>
   </si>
   <si>
+    <t>prevencion.araucania22@gmail.com</t>
+  </si>
+  <si>
     <t>Rodolfo Vidal</t>
   </si>
   <si>
+    <t>o.vidalparada@gmail.com</t>
+  </si>
+  <si>
     <t>Lucas García</t>
   </si>
   <si>
+    <t>patogarciallancaleo@gmail.com</t>
+  </si>
+  <si>
     <t>Nicolas Garcia</t>
   </si>
   <si>
@@ -474,6 +498,9 @@
     <t>Dante Galarce</t>
   </si>
   <si>
+    <t>dm.elgueta@gmail.com</t>
+  </si>
+  <si>
     <t>Sebastian Curiqueo</t>
   </si>
   <si>
@@ -588,6 +615,9 @@
     <t>Leonardo Huentemil</t>
   </si>
   <si>
+    <t>leonardohuentemil661@gmail.com</t>
+  </si>
+  <si>
     <t>Ignacio Perez</t>
   </si>
   <si>
@@ -765,17 +795,35 @@
     <t>JOSEFINA OTAROLA</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>josefiinaotarola@gmail.com</t>
+    </r>
+  </si>
+  <si>
     <t>ANDREA ESPINOZA</t>
   </si>
   <si>
     <t>MARISELA PASCUAL</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>chxndmr@gmail.com</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="6">
+  <fonts count="8">
     <font>
       <sz val="11.0"/>
       <color theme="1"/>
@@ -786,6 +834,11 @@
       <sz val="10.0"/>
       <color theme="1"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -804,6 +857,10 @@
       <u/>
       <color rgb="FF0000FF"/>
     </font>
+    <font>
+      <u/>
+      <color rgb="FF0000FF"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -813,7 +870,7 @@
       <patternFill patternType="lightGray"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border/>
     <border>
       <left style="thin">
@@ -840,11 +897,16 @@
         <color rgb="FF000000"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="20">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -852,11 +914,15 @@
     <xf borderId="1" fillId="0" fontId="1" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="3" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -865,20 +931,30 @@
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="1" fillId="0" fontId="1" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right"/>
+      <alignment horizontal="right" readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
@@ -1121,1855 +1197,2132 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="2" ht="14.25" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>9</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I2" s="5"/>
     </row>
     <row r="3" ht="14.25" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="4" t="s">
         <v>11</v>
       </c>
+      <c r="B3" s="6" t="s">
+        <v>12</v>
+      </c>
       <c r="C3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1">
       <c r="A5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="5" t="s">
         <v>14</v>
       </c>
+      <c r="B5" s="7" t="s">
+        <v>15</v>
+      </c>
       <c r="C5" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>9</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="B6" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>17</v>
+      <c r="C6" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" s="5" t="s">
         <v>19</v>
       </c>
+      <c r="B7" s="7" t="s">
+        <v>20</v>
+      </c>
       <c r="C7" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1">
       <c r="A8" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B8" s="5" t="s">
         <v>21</v>
       </c>
+      <c r="B8" s="7" t="s">
+        <v>22</v>
+      </c>
       <c r="C8" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="9" ht="14.25" customHeight="1">
       <c r="A9" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B9" s="5" t="s">
         <v>23</v>
       </c>
+      <c r="B9" s="7" t="s">
+        <v>24</v>
+      </c>
       <c r="C9" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="10" ht="14.25" customHeight="1">
       <c r="A10" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B10" s="4" t="s">
         <v>25</v>
       </c>
+      <c r="B10" s="6" t="s">
+        <v>26</v>
+      </c>
       <c r="C10" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="11" ht="14.25" customHeight="1">
       <c r="A11" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B11" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C11" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="G11" s="6" t="s">
-        <v>17</v>
+      <c r="B11" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="12" ht="14.25" customHeight="1">
       <c r="A12" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="13" ht="14.25" customHeight="1">
       <c r="A13" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B13" s="4" t="s">
         <v>30</v>
       </c>
+      <c r="B13" s="6" t="s">
+        <v>31</v>
+      </c>
       <c r="C13" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="14" ht="14.25" customHeight="1">
       <c r="A14" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B14" s="7"/>
+        <v>32</v>
+      </c>
+      <c r="B14" s="9"/>
       <c r="C14" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>9</v>
+        <v>9</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="15" ht="14.25" customHeight="1">
       <c r="A15" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B15" s="5" t="s">
         <v>33</v>
       </c>
+      <c r="B15" s="7" t="s">
+        <v>34</v>
+      </c>
       <c r="C15" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="16" ht="14.25" customHeight="1">
-      <c r="A16" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="B16" s="4" t="s">
+      <c r="A16" s="10" t="s">
         <v>35</v>
       </c>
+      <c r="B16" s="6" t="s">
+        <v>36</v>
+      </c>
       <c r="C16" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="17" ht="14.25" customHeight="1">
-      <c r="A17" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B17" s="4" t="s">
+      <c r="A17" s="10" t="s">
         <v>37</v>
       </c>
+      <c r="B17" s="6" t="s">
+        <v>38</v>
+      </c>
       <c r="C17" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="F17" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="18" ht="14.25" customHeight="1">
       <c r="A18" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B18" s="7"/>
+        <v>39</v>
+      </c>
+      <c r="B18" s="9"/>
       <c r="C18" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="19" ht="14.25" customHeight="1">
       <c r="A19" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B19" s="5" t="s">
         <v>40</v>
       </c>
+      <c r="B19" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="C19" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="20" ht="14.25" customHeight="1">
       <c r="A20" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B20" s="9" t="s">
         <v>42</v>
       </c>
+      <c r="B20" s="12" t="s">
+        <v>43</v>
+      </c>
       <c r="C20" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="21" ht="14.25" customHeight="1">
       <c r="A21" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="22" ht="14.25" customHeight="1">
       <c r="A22" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B22" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="C22" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D22" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E22" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F22" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="G22" s="6" t="s">
-        <v>17</v>
+      <c r="B22" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G22" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H22" s="8" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="23" ht="14.25" customHeight="1">
       <c r="A23" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B23" s="5" t="s">
         <v>47</v>
       </c>
+      <c r="B23" s="7" t="s">
+        <v>48</v>
+      </c>
       <c r="C23" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="24" ht="14.25" customHeight="1">
       <c r="A24" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B24" s="7"/>
+        <v>49</v>
+      </c>
+      <c r="B24" s="9"/>
       <c r="C24" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="25" ht="14.25" customHeight="1">
       <c r="A25" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B25" s="5" t="s">
         <v>50</v>
       </c>
+      <c r="B25" s="7" t="s">
+        <v>51</v>
+      </c>
       <c r="C25" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="26" ht="14.25" customHeight="1">
       <c r="A26" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B26" s="5" t="s">
         <v>52</v>
       </c>
+      <c r="B26" s="7" t="s">
+        <v>53</v>
+      </c>
       <c r="C26" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="27" ht="14.25" customHeight="1">
       <c r="A27" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B27" s="4" t="s">
         <v>54</v>
       </c>
+      <c r="B27" s="6" t="s">
+        <v>55</v>
+      </c>
       <c r="C27" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>9</v>
+        <v>9</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="28" ht="14.25" customHeight="1">
       <c r="A28" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B28" s="7"/>
+        <v>56</v>
+      </c>
+      <c r="B28" s="9"/>
       <c r="C28" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>9</v>
+        <v>9</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="29" ht="14.25" customHeight="1">
       <c r="A29" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B29" s="4" t="s">
         <v>57</v>
       </c>
+      <c r="B29" s="6" t="s">
+        <v>58</v>
+      </c>
       <c r="C29" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="30" ht="14.25" customHeight="1">
       <c r="A30" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B30" s="5" t="s">
         <v>59</v>
       </c>
+      <c r="B30" s="7" t="s">
+        <v>60</v>
+      </c>
       <c r="C30" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="31" ht="14.25" customHeight="1">
       <c r="A31" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B31" s="4" t="s">
         <v>61</v>
       </c>
+      <c r="B31" s="6" t="s">
+        <v>62</v>
+      </c>
       <c r="C31" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>9</v>
+        <v>9</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="32" ht="14.25" customHeight="1">
       <c r="A32" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B32" s="4" t="s">
         <v>63</v>
       </c>
+      <c r="B32" s="6" t="s">
+        <v>64</v>
+      </c>
       <c r="C32" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>9</v>
+        <v>9</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="33" ht="14.25" customHeight="1">
       <c r="A33" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B33" s="5" t="s">
         <v>65</v>
       </c>
+      <c r="B33" s="7" t="s">
+        <v>66</v>
+      </c>
       <c r="C33" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>9</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="34" ht="14.25" customHeight="1">
       <c r="A34" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B34" s="7"/>
+        <v>67</v>
+      </c>
+      <c r="B34" s="9"/>
       <c r="C34" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>9</v>
+        <v>9</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="35" ht="14.25" customHeight="1">
       <c r="A35" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B35" s="2"/>
       <c r="C35" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="36" ht="14.25" customHeight="1">
       <c r="A36" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B36" s="7"/>
+        <v>69</v>
+      </c>
+      <c r="B36" s="9"/>
       <c r="C36" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>9</v>
+        <v>9</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="37" ht="14.25" customHeight="1">
-      <c r="A37" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="B37" s="4" t="s">
+      <c r="A37" s="10" t="s">
         <v>70</v>
       </c>
+      <c r="B37" s="6" t="s">
+        <v>71</v>
+      </c>
       <c r="C37" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>9</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="H37" s="13"/>
     </row>
     <row r="38" ht="14.25" customHeight="1">
-      <c r="A38" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="B38" s="5" t="s">
+      <c r="A38" s="10" t="s">
         <v>72</v>
       </c>
+      <c r="B38" s="7" t="s">
+        <v>73</v>
+      </c>
       <c r="C38" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="39" ht="14.25" customHeight="1">
-      <c r="A39" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="B39" s="4" t="s">
+      <c r="A39" s="10" t="s">
         <v>74</v>
       </c>
+      <c r="B39" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="C39" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="40" ht="14.25" customHeight="1">
-      <c r="A40" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="B40" s="10"/>
+      <c r="A40" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="B40" s="14" t="s">
+        <v>77</v>
+      </c>
       <c r="C40" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D40" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D40" s="8" t="s">
         <v>9</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="41" ht="14.25" customHeight="1">
-      <c r="A41" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="B41" s="10"/>
+      <c r="A41" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="B41" s="14" t="s">
+        <v>77</v>
+      </c>
       <c r="C41" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="42" ht="14.25" customHeight="1">
-      <c r="A42" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="B42" s="10"/>
+      <c r="A42" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="B42" s="14" t="s">
+        <v>80</v>
+      </c>
       <c r="C42" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F42" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G42" s="1" t="s">
-        <v>9</v>
+        <v>9</v>
+      </c>
+      <c r="F42" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G42" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="43" ht="14.25" customHeight="1">
-      <c r="A43" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="B43" s="10"/>
+      <c r="A43" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="B43" s="14" t="s">
+        <v>82</v>
+      </c>
       <c r="C43" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="44" ht="14.25" customHeight="1">
-      <c r="A44" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="B44" s="10"/>
+      <c r="A44" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="B44" s="15"/>
       <c r="C44" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F44" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F44" s="8" t="s">
         <v>9</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="45" ht="14.25" customHeight="1">
-      <c r="A45" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="B45" s="10"/>
+      <c r="A45" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="B45" s="14" t="s">
+        <v>85</v>
+      </c>
       <c r="C45" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F45" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G45" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="F45" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G45" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="46" ht="14.25" customHeight="1">
-      <c r="A46" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="B46" s="10"/>
+      <c r="A46" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="B46" s="15"/>
       <c r="C46" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="47" ht="14.25" customHeight="1">
-      <c r="A47" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="B47" s="10"/>
+      <c r="A47" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="B47" s="14" t="s">
+        <v>88</v>
+      </c>
       <c r="C47" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F47" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G47" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F47" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G47" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="H47" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="48" ht="14.25" customHeight="1">
-      <c r="A48" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="B48" s="10"/>
+      <c r="A48" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="B48" s="14" t="s">
+        <v>90</v>
+      </c>
       <c r="C48" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="49" ht="14.25" customHeight="1">
-      <c r="A49" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="B49" s="10"/>
+      <c r="A49" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="B49" s="14" t="s">
+        <v>92</v>
+      </c>
       <c r="C49" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="50" ht="14.25" customHeight="1">
-      <c r="A50" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="B50" s="10"/>
+      <c r="A50" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="B50" s="14" t="s">
+        <v>92</v>
+      </c>
       <c r="C50" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="H50" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="51" ht="14.25" customHeight="1">
-      <c r="A51" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="B51" s="4" t="s">
-        <v>87</v>
+      <c r="A51" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>95</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="H51" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="52" ht="14.25" customHeight="1">
-      <c r="A52" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="B52" s="10"/>
+      <c r="A52" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="B52" s="15"/>
       <c r="C52" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="53" ht="14.25" customHeight="1">
-      <c r="A53" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="B53" s="4" t="s">
-        <v>90</v>
+      <c r="A53" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>98</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="H53" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="54" ht="14.25" customHeight="1">
-      <c r="A54" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="B54" s="4" t="s">
-        <v>92</v>
+      <c r="A54" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>100</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="55" ht="14.25" customHeight="1">
-      <c r="A55" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="B55" s="10"/>
+      <c r="A55" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="B55" s="14" t="s">
+        <v>102</v>
+      </c>
       <c r="C55" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="H55" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="56" ht="14.25" customHeight="1">
       <c r="A56" s="1" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F56" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="F56" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="H56" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="57" ht="14.25" customHeight="1">
       <c r="A57" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="B57" s="4" t="s">
-        <v>96</v>
+        <v>104</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>105</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F57" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="F57" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="58" ht="14.25" customHeight="1">
       <c r="A58" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="B58" s="4" t="s">
-        <v>98</v>
+        <v>106</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>107</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="F58" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="59" ht="14.25" customHeight="1">
       <c r="A59" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="B59" s="4" t="s">
-        <v>100</v>
+        <v>108</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>109</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="F59" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="60" ht="14.25" customHeight="1">
       <c r="A60" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="B60" s="4" t="s">
-        <v>102</v>
+        <v>110</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>111</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F60" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="F60" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="61" ht="14.25" customHeight="1">
       <c r="A61" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="B61" s="4" t="s">
-        <v>104</v>
+        <v>112</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>113</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F61" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="F61" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="H61" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="62" ht="14.25" customHeight="1">
       <c r="A62" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="B62" s="4" t="s">
-        <v>106</v>
+        <v>114</v>
+      </c>
+      <c r="B62" s="6" t="s">
+        <v>115</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F62" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="F62" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="63" ht="14.25" customHeight="1">
       <c r="A63" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="B63" s="4" t="s">
-        <v>108</v>
+        <v>116</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>117</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F63" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="F63" s="4" t="s">
+        <v>9</v>
       </c>
       <c r="G63" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H63" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="64" ht="14.25" customHeight="1">
       <c r="A64" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="B64" s="4" t="s">
-        <v>110</v>
+        <v>118</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>119</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F64" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="F64" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="H64" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="65" ht="14.25" customHeight="1">
       <c r="A65" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="B65" s="4" t="s">
-        <v>112</v>
+        <v>120</v>
+      </c>
+      <c r="B65" s="6" t="s">
+        <v>121</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F65" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="F65" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="H65" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="66" ht="14.25" customHeight="1">
       <c r="A66" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="B66" s="11"/>
-      <c r="C66" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D66" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E66" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F66" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B66" s="16" t="s">
+        <v>123</v>
+      </c>
+      <c r="C66" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D66" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E66" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F66" s="11" t="s">
         <v>9</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="67" ht="14.25" customHeight="1">
       <c r="A67" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="B67" s="4" t="s">
-        <v>115</v>
+        <v>124</v>
+      </c>
+      <c r="B67" s="6" t="s">
+        <v>125</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F67" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="F67" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="H67" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="68" ht="14.25" customHeight="1">
       <c r="A68" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="B68" s="4" t="s">
-        <v>117</v>
+        <v>126</v>
+      </c>
+      <c r="B68" s="6" t="s">
+        <v>127</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F68" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="F68" s="4" t="s">
+        <v>9</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="H68" s="3" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="69" ht="14.25" customHeight="1">
-      <c r="A69" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="B69" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="C69" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D69" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E69" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F69" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="G69" s="8" t="s">
-        <v>8</v>
+      <c r="A69" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="B69" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="C69" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D69" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E69" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F69" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G69" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="H69" s="3" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="70" ht="14.25" customHeight="1">
-      <c r="A70" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="B70" s="12" t="s">
-        <v>121</v>
-      </c>
-      <c r="C70" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D70" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E70" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F70" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="G70" s="8" t="s">
+      <c r="A70" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="B70" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="C70" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D70" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E70" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F70" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G70" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="H70" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="71" ht="14.25" customHeight="1">
-      <c r="A71" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="B71" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="C71" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="D71" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E71" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F71" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="G71" s="8" t="s">
+      <c r="A71" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="B71" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="C71" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="D71" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="E71" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="F71" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="G71" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="H71" s="18" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="72" ht="14.25" customHeight="1">
-      <c r="A72" s="8" t="s">
-        <v>124</v>
-      </c>
-      <c r="B72" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="C72" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="D72" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E72" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F72" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="G72" s="8" t="s">
-        <v>9</v>
+      <c r="A72" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="B72" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C72" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D72" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E72" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F72" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G72" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="73" ht="14.25" customHeight="1">
-      <c r="A73" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="B73" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="C73" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="D73" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E73" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F73" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="G73" s="8" t="s">
-        <v>9</v>
+      <c r="A73" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="B73" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="C73" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D73" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E73" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F73" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G73" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H73" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="74" ht="14.25" customHeight="1">
-      <c r="A74" s="8" t="s">
-        <v>128</v>
-      </c>
-      <c r="B74" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="C74" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="D74" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E74" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F74" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="G74" s="8" t="s">
-        <v>9</v>
+      <c r="A74" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="B74" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="C74" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D74" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E74" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F74" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G74" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H74" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="75" ht="14.25" customHeight="1">
-      <c r="A75" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="B75" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="C75" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D75" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E75" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F75" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="G75" s="8" t="s">
-        <v>8</v>
+      <c r="A75" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="B75" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="C75" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D75" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E75" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F75" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G75" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="H75" s="3" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="76" ht="14.25" customHeight="1">
-      <c r="A76" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="B76" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="C76" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="D76" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E76" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F76" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="G76" s="8" t="s">
-        <v>9</v>
+      <c r="A76" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="B76" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="C76" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D76" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E76" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F76" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G76" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H76" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="77" ht="14.25" customHeight="1">
-      <c r="A77" s="8" t="s">
-        <v>134</v>
-      </c>
-      <c r="B77" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="C77" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D77" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E77" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F77" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="G77" s="8" t="s">
-        <v>8</v>
+      <c r="A77" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="B77" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="C77" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D77" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E77" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F77" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G77" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="H77" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="78" ht="14.25" customHeight="1">
-      <c r="A78" s="8" t="s">
-        <v>136</v>
-      </c>
-      <c r="B78" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="C78" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D78" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E78" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F78" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="G78" s="8" t="s">
+      <c r="A78" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="B78" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="C78" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D78" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E78" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F78" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G78" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H78" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="79" ht="14.25" customHeight="1">
-      <c r="A79" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="B79" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="C79" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D79" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E79" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F79" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="G79" s="8" t="s">
+      <c r="A79" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="B79" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="C79" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D79" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E79" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F79" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G79" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H79" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="80" ht="14.25" customHeight="1">
-      <c r="A80" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="B80" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="C80" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D80" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E80" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F80" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="G80" s="8" t="s">
-        <v>8</v>
+      <c r="A80" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="B80" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="C80" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D80" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E80" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F80" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G80" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="H80" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="81" ht="14.25" customHeight="1">
-      <c r="A81" s="8" t="s">
-        <v>142</v>
-      </c>
-      <c r="B81" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="C81" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D81" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E81" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F81" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="G81" s="8" t="s">
-        <v>9</v>
+      <c r="A81" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="B81" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="C81" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D81" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E81" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F81" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G81" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="82" ht="14.25" customHeight="1">
-      <c r="A82" s="8" t="s">
-        <v>144</v>
-      </c>
-      <c r="B82" s="8"/>
-      <c r="C82" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D82" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E82" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F82" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="G82" s="8" t="s">
-        <v>9</v>
+      <c r="A82" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="B82" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="C82" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D82" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E82" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F82" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G82" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H82" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="83" ht="14.25" customHeight="1">
-      <c r="A83" s="8" t="s">
-        <v>145</v>
-      </c>
-      <c r="B83" s="8"/>
-      <c r="C83" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="D83" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="E83" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="F83" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="G83" s="13" t="s">
-        <v>17</v>
+      <c r="A83" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="B83" s="10"/>
+      <c r="C83" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="D83" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="E83" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="F83" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="G83" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="H83" s="18" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="84" ht="14.25" customHeight="1">
-      <c r="A84" s="8" t="s">
-        <v>146</v>
-      </c>
-      <c r="B84" s="8"/>
-      <c r="C84" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D84" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E84" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F84" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="G84" s="8" t="s">
-        <v>9</v>
+      <c r="A84" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="B84" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="C84" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D84" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E84" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F84" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G84" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H84" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="85" ht="14.25" customHeight="1"/>
@@ -3943,10 +4296,12 @@
     <hyperlink r:id="rId51" ref="B79"/>
     <hyperlink r:id="rId52" ref="B80"/>
     <hyperlink r:id="rId53" ref="B81"/>
+    <hyperlink r:id="rId54" ref="B82"/>
+    <hyperlink r:id="rId55" ref="B84"/>
   </hyperlinks>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId54"/>
+  <drawing r:id="rId56"/>
 </worksheet>
 </file>